--- a/ProjectDocs/Requirements_Backlog.xlsx
+++ b/ProjectDocs/Requirements_Backlog.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,58 +425,103 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:S101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Issue Key</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Story Points</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Design Summary</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>UI Fields</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>API/Service</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Data Rules</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Security/Compliance</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
         </is>
       </c>
     </row>
@@ -489,10 +546,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E2" t="n">
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -517,6 +572,51 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>All required fields validate and save</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Capture applicant profile: Create profile form with required fields. AC: All required fields validate and save.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -541,10 +641,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E3" t="n">
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -569,6 +667,51 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>Draft saved and can be resumed</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Save draft enrollment: Allow saving draft application. AC: Draft saved and can be resumed.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -593,10 +736,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E4" t="n">
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -621,6 +762,51 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>Edits persist and reflect in review</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Edit profile data: Allow edits before submission. AC: Edits persist and reflect in review.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -645,10 +831,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E5" t="n">
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -673,6 +857,51 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>Masked display with secure storage</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Field masking: Mask SSN and DOB inputs. AC: Masked display with secure storage.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -697,10 +926,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E6" t="n">
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -725,6 +952,51 @@
       <c r="J6" t="inlineStr">
         <is>
           <t>Valid matches pass, invalid fail</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SSN and DOB validation: Validate SSN and DOB with registry. AC: Valid matches pass, invalid fail.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ssn_last4,dob,match_status,attempt_count</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>POST /members/{id}/identity-check, GET /members/{id}/identity-audit</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -749,10 +1021,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E7" t="n">
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -777,6 +1047,51 @@
       <c r="J7" t="inlineStr">
         <is>
           <t>Max retries enforced</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Identity retry rules: Allow limited retries. AC: Max retries enforced.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ssn_last4,dob,match_status,attempt_count</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>POST /members/{id}/identity-check, GET /members/{id}/identity-audit</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -801,10 +1116,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E8" t="n">
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -829,6 +1142,51 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>Partial matches flagged for review</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Partial match handling: Handle partial matches. AC: Partial matches flagged for review.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ssn_last4,dob,match_status,attempt_count</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>POST /members/{id}/identity-check, GET /members/{id}/identity-audit</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -853,10 +1211,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E9" t="n">
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -881,6 +1237,51 @@
       <c r="J9" t="inlineStr">
         <is>
           <t>Audit log includes user and timestamp</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Audit identity checks: Log identity checks. AC: Audit log includes user and timestamp.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -905,10 +1306,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E10" t="n">
+        <v>5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -933,6 +1332,51 @@
       <c r="J10" t="inlineStr">
         <is>
           <t>Response mapped to app status</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Eligibility API integration: Call eligibility service. AC: Response mapped to app status.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>member_id,eligibility_status,reason_code</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>POST /eligibility/check, POST /eligibility/submit</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -957,10 +1401,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E11" t="n">
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -985,6 +1427,51 @@
       <c r="J11" t="inlineStr">
         <is>
           <t>Retries follow backoff and stop</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Retry on eligibility timeout: Retry eligibility up to 2 times. AC: Retries follow backoff and stop.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>member_id,eligibility_status,reason_code</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>POST /eligibility/check, POST /eligibility/submit</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1009,10 +1496,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E12" t="n">
+        <v>5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1037,6 +1522,51 @@
       <c r="J12" t="inlineStr">
         <is>
           <t>Codes displayed and stored</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Eligibility code mapping: Map payer codes to UI. AC: Codes displayed and stored.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>member_id,eligibility_status,reason_code</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>POST /eligibility/check, POST /eligibility/submit</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1061,10 +1591,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E13" t="n">
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1089,6 +1617,51 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>User sees actionable message</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Eligibility error messaging: Show clear errors. AC: User sees actionable message.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>channel,email,phone,template_id</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>POST /notifications/send, GET /notifications/{id}</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1113,10 +1686,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E14" t="n">
+        <v>5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1141,6 +1712,51 @@
       <c r="J14" t="inlineStr">
         <is>
           <t>Plans list matches backend</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Plan catalog listing: Display plans with premiums. AC: Plans list matches backend.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>plan_id,plan_tier,premium,coverage_summary</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>GET /plans, GET /plans/{id}</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1781,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E15" t="n">
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1193,6 +1807,51 @@
       <c r="J15" t="inlineStr">
         <is>
           <t>Filters update results</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Plan tier filtering: Filter by tier. AC: Filters update results.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>plan_id,plan_tier,premium,coverage_summary</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>GET /plans, GET /plans/{id}</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1217,10 +1876,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E16" t="n">
+        <v>3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1245,6 +1902,51 @@
       <c r="J16" t="inlineStr">
         <is>
           <t>Comparison shows key fields</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Plan comparison: Compare plan benefits. AC: Comparison shows key fields.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>plan_id,plan_tier,premium,coverage_summary</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>GET /plans, GET /plans/{id}</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1269,10 +1971,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E17" t="n">
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1297,6 +1997,51 @@
       <c r="J17" t="inlineStr">
         <is>
           <t>Summary visible before selection</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Coverage summary: Show coverage highlights. AC: Summary visible before selection.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>plan_id,plan_tier,premium,coverage_summary</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>GET /plans, GET /plans/{id}</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1321,10 +2066,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E18" t="n">
+        <v>5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1349,6 +2092,51 @@
       <c r="J18" t="inlineStr">
         <is>
           <t>Files upload within size limits</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Document upload: Upload PDF/JPG/PNG. AC: Files upload within size limits.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>document_type,file_name,file_size,upload_status</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>POST /documents, GET /documents/{id}</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1373,10 +2161,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E19" t="n">
+        <v>2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1401,6 +2187,51 @@
       <c r="J19" t="inlineStr">
         <is>
           <t>Invalid files blocked</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>File type validation: Reject unsupported formats. AC: Invalid files blocked.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>document_type,file_name,file_size,upload_status</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>POST /documents, GET /documents/{id}</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1425,10 +2256,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E20" t="n">
+        <v>2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1453,6 +2282,51 @@
       <c r="J20" t="inlineStr">
         <is>
           <t>Progress updates during upload</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Upload progress: Show progress bar. AC: Progress updates during upload.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>document_type,file_name,file_size,upload_status</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>POST /documents, GET /documents/{id}</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1477,10 +2351,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E21" t="n">
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1505,6 +2377,51 @@
       <c r="J21" t="inlineStr">
         <is>
           <t>Metadata saved and visible</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Document metadata: Store doc type and timestamp. AC: Metadata saved and visible.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>document_type,file_name,file_size,upload_status</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>POST /documents, GET /documents/{id}</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1529,10 +2446,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E22" t="n">
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1557,6 +2472,51 @@
       <c r="J22" t="inlineStr">
         <is>
           <t>Email sent on submit</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Email confirmation: Send confirmation email. AC: Email sent on submit.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>channel,email,phone,template_id</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>POST /notifications/send, GET /notifications/{id}</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1581,10 +2541,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E23" t="n">
+        <v>3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1609,6 +2567,51 @@
       <c r="J23" t="inlineStr">
         <is>
           <t>Opt-in stored with timestamp</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>SMS opt-in: Capture SMS consent. AC: Opt-in stored with timestamp.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>channel,email,phone,template_id</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>POST /notifications/send, GET /notifications/{id}</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1633,10 +2636,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E24" t="n">
+        <v>2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1661,6 +2662,51 @@
       <c r="J24" t="inlineStr">
         <is>
           <t>Templates render correctly</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Template variables: Support dynamic fields. AC: Templates render correctly.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>channel,email,phone,template_id</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>POST /notifications/send, GET /notifications/{id}</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1685,10 +2731,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E25" t="n">
+        <v>2</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1713,6 +2757,51 @@
       <c r="J25" t="inlineStr">
         <is>
           <t>Audit entries created</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Notification audit log: Log sends. AC: Audit entries created.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1737,10 +2826,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E26" t="n">
+        <v>5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1765,6 +2852,51 @@
       <c r="J26" t="inlineStr">
         <is>
           <t>Dependent saved and listed</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Add dependent: Add dependent details. AC: Dependent saved and listed.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1789,10 +2921,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E27" t="n">
+        <v>3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1817,6 +2947,51 @@
       <c r="J27" t="inlineStr">
         <is>
           <t>Errors for invalid ages</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Dependent age rules: Validate dependent age. AC: Errors for invalid ages.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>member_id,eligibility_status,reason_code</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>POST /eligibility/check, POST /eligibility/submit</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1841,10 +3016,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E28" t="n">
+        <v>3</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1869,6 +3042,51 @@
       <c r="J28" t="inlineStr">
         <is>
           <t>Only allowed values accepted</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Relationship validation: Validate relationship type. AC: Only allowed values accepted.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1893,10 +3111,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E29" t="n">
+        <v>2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1921,6 +3137,51 @@
       <c r="J29" t="inlineStr">
         <is>
           <t>Dependent removed from draft</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Dependent removal: Remove dependent. AC: Dependent removed from draft.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1945,10 +3206,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E30" t="n">
+        <v>5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1973,6 +3232,51 @@
       <c r="J30" t="inlineStr">
         <is>
           <t>Valid addresses normalized</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>USPS validation: Validate address via USPS. AC: Valid addresses normalized.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -1997,10 +3301,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E31" t="n">
+        <v>3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2025,6 +3327,51 @@
       <c r="J31" t="inlineStr">
         <is>
           <t>Override logged and saved</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Address override: Allow manual override. AC: Override logged and saved.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2049,10 +3396,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E32" t="n">
+        <v>2</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2077,6 +3422,51 @@
       <c r="J32" t="inlineStr">
         <is>
           <t>User can accept suggestion</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Address suggestions: Suggest corrections. AC: User can accept suggestion.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2101,10 +3491,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E33" t="n">
+        <v>2</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2129,6 +3517,51 @@
       <c r="J33" t="inlineStr">
         <is>
           <t>Audit entry created</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Audit address change: Log address changes. AC: Audit entry created.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2153,10 +3586,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E34" t="n">
+        <v>5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2181,6 +3612,51 @@
       <c r="J34" t="inlineStr">
         <is>
           <t>Consent stored with version</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>HIPAA consent: Capture HIPAA consent. AC: Consent stored with version.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2205,10 +3681,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E35" t="n">
+        <v>3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2233,6 +3707,51 @@
       <c r="J35" t="inlineStr">
         <is>
           <t>Version stored per user</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Consent versioning: Track consent version. AC: Version stored per user.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2257,10 +3776,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E36" t="n">
+        <v>3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2285,6 +3802,51 @@
       <c r="J36" t="inlineStr">
         <is>
           <t>Audit includes user/time</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Consent audit trail: Log consent events. AC: Audit includes user/time.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2309,10 +3871,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E37" t="n">
+        <v>2</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2337,6 +3897,51 @@
       <c r="J37" t="inlineStr">
         <is>
           <t>Summary visible before submit</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Consent display: Show consent summary. AC: Summary visible before submit.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2361,10 +3966,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E38" t="n">
+        <v>5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2389,6 +3992,51 @@
       <c r="J38" t="inlineStr">
         <is>
           <t>Payment token stored</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Payment profile create: Add payment method. AC: Payment token stored.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>payment_method,token,last4,amount</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>POST /payments, GET /payments/{id}</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2413,10 +4061,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E39" t="n">
+        <v>5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2441,6 +4087,51 @@
       <c r="J39" t="inlineStr">
         <is>
           <t>Estimate matches rules</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Premium estimate: Calculate premium. AC: Estimate matches rules.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>payment_method,token,last4,amount</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>POST /payments, GET /payments/{id}</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2465,10 +4156,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E40" t="n">
+        <v>3</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2493,6 +4182,51 @@
       <c r="J40" t="inlineStr">
         <is>
           <t>Retry logic applied</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Payment retry: Retry failed payments. AC: Retry logic applied.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>payment_method,token,last4,amount</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>POST /payments, GET /payments/{id}</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2517,10 +4251,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E41" t="n">
+        <v>2</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2545,6 +4277,51 @@
       <c r="J41" t="inlineStr">
         <is>
           <t>Confirmation delivered</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Payment confirmation: Notify on payment. AC: Confirmation delivered.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>channel,email,phone,template_id</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>POST /notifications/send, GET /notifications/{id}</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2569,10 +4346,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E42" t="n">
+        <v>5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2597,6 +4372,51 @@
       <c r="J42" t="inlineStr">
         <is>
           <t>Payload accepted by API</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Submission payload: Submit payload to payer. AC: Payload accepted by API.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>member_id,eligibility_status,reason_code</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>POST /eligibility/check, POST /eligibility/submit</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2621,10 +4441,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E43" t="n">
+        <v>3</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2649,6 +4467,51 @@
       <c r="J43" t="inlineStr">
         <is>
           <t>Duplicate requests rejected</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Idempotent submission: Prevent duplicate submissions. AC: Duplicate requests rejected.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>member_id,eligibility_status,reason_code</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>POST /eligibility/check, POST /eligibility/submit</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2673,10 +4536,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E44" t="n">
+        <v>3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2701,6 +4562,51 @@
       <c r="J44" t="inlineStr">
         <is>
           <t>Errors visible with retry</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Submission error handling: Show submission errors. AC: Errors visible with retry.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>channel,email,phone,template_id</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>POST /notifications/send, GET /notifications/{id}</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2725,10 +4631,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E45" t="n">
+        <v>2</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2753,6 +4657,51 @@
       <c r="J45" t="inlineStr">
         <is>
           <t>Audit includes response code</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Submission audit: Log submission events. AC: Audit includes response code.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2777,10 +4726,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E46" t="n">
+        <v>5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2805,6 +4752,51 @@
       <c r="J46" t="inlineStr">
         <is>
           <t>All sections visible</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Review page: Show review summary. AC: All sections visible.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2829,10 +4821,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E47" t="n">
+        <v>3</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2857,6 +4847,51 @@
       <c r="J47" t="inlineStr">
         <is>
           <t>Edits persist and refresh</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Inline edit: Edit from review. AC: Edits persist and refresh.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2881,10 +4916,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E48" t="n">
+        <v>3</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2909,6 +4942,51 @@
       <c r="J48" t="inlineStr">
         <is>
           <t>Errors highlighted</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Review validations: Block submit on errors. AC: Errors highlighted.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2933,10 +5011,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E49" t="n">
+        <v>2</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2961,6 +5037,51 @@
       <c r="J49" t="inlineStr">
         <is>
           <t>PDF generated</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Review download: Download summary PDF. AC: PDF generated.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>document_type,file_name,file_size,upload_status</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>POST /documents, GET /documents/{id}</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -2985,10 +5106,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E50" t="n">
+        <v>5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3013,6 +5132,51 @@
       <c r="J50" t="inlineStr">
         <is>
           <t>Status refreshes on interval</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Enrollment status: Show status from payer. AC: Status refreshes on interval.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3037,10 +5201,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E51" t="n">
+        <v>3</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3065,6 +5227,51 @@
       <c r="J51" t="inlineStr">
         <is>
           <t>Email sent on update</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Status notifications: Notify on status change. AC: Email sent on update.</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>channel,email,phone,template_id</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>POST /notifications/send, GET /notifications/{id}</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3089,10 +5296,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E52" t="n">
+        <v>3</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3117,6 +5322,51 @@
       <c r="J52" t="inlineStr">
         <is>
           <t>Reason stored and shown</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Rejection reasons: Display rejection reason. AC: Reason stored and shown.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3141,10 +5391,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E53" t="n">
+        <v>2</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3169,6 +5417,51 @@
       <c r="J53" t="inlineStr">
         <is>
           <t>History visible to CSR</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Status history: Keep status history. AC: History visible to CSR.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3193,10 +5486,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E54" t="n">
+        <v>5</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3221,6 +5512,51 @@
       <c r="J54" t="inlineStr">
         <is>
           <t>CSR flow mirrors member flow</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>CSR assisted flow: CSR can create enrollment. AC: CSR flow mirrors member flow.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>csr_id,member_id,status,notes</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>GET /csr/queue, POST /csr/notes</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3245,10 +5581,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E55" t="n">
+        <v>3</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3273,6 +5607,51 @@
       <c r="J55" t="inlineStr">
         <is>
           <t>Notes stored with audit</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>CSR notes: Allow CSR notes. AC: Notes stored with audit.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>csr_id,member_id,status,notes</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>GET /csr/queue, POST /csr/notes</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3297,10 +5676,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E56" t="n">
+        <v>5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3325,6 +5702,51 @@
       <c r="J56" t="inlineStr">
         <is>
           <t>Access limited to CSR role</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Role-based access: Restrict CSR tools. AC: Access limited to CSR role.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3349,10 +5771,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E57" t="n">
+        <v>3</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3377,6 +5797,51 @@
       <c r="J57" t="inlineStr">
         <is>
           <t>Search by member and status</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>CSR search: Search applications. AC: Search by member and status.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>csr_id,member_id,status,notes</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>GET /csr/queue, POST /csr/notes</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3401,10 +5866,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E58" t="n">
+        <v>3</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3429,6 +5892,51 @@
       <c r="J58" t="inlineStr">
         <is>
           <t>Preference saved and reused</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Language preferences: Store language setting. AC: Preference saved and reused.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3453,10 +5961,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E59" t="n">
+        <v>3</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3481,6 +5987,51 @@
       <c r="J59" t="inlineStr">
         <is>
           <t>Spanish labels visible</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Translation coverage: Translate key labels. AC: Spanish labels visible.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3505,10 +6056,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E60" t="n">
+        <v>5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3533,6 +6082,51 @@
       <c r="J60" t="inlineStr">
         <is>
           <t>Screen reader passes</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Accessibility labels: Add aria labels. AC: Screen reader passes.</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3557,10 +6151,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E61" t="n">
+        <v>2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3585,6 +6177,51 @@
       <c r="J61" t="inlineStr">
         <is>
           <t>All fields accessible</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Keyboard navigation: Tab order logical. AC: All fields accessible.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3609,10 +6246,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E62" t="n">
+        <v>5</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3637,6 +6272,51 @@
       <c r="J62" t="inlineStr">
         <is>
           <t>Duplicates flagged</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Duplicate detection: Detect duplicate applications. AC: Duplicates flagged.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3661,10 +6341,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E63" t="n">
+        <v>3</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3689,6 +6367,51 @@
       <c r="J63" t="inlineStr">
         <is>
           <t>Scores stored in audit</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Fraud scoring: Score suspicious submissions. AC: Scores stored in audit.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3713,10 +6436,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E64" t="n">
+        <v>3</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3741,6 +6462,51 @@
       <c r="J64" t="inlineStr">
         <is>
           <t>CSR can review and decide</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Manual review queue: Queue flagged apps. AC: CSR can review and decide.</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>csr_id,member_id,status,notes</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>GET /csr/queue, POST /csr/notes</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3765,10 +6531,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E65" t="n">
+        <v>2</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3793,6 +6557,51 @@
       <c r="J65" t="inlineStr">
         <is>
           <t>Warning shown to user</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Duplicate warnings: Warn on duplicate submit. AC: Warning shown to user.</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>channel,email,phone,template_id</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>POST /notifications/send, GET /notifications/{id}</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3817,10 +6626,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E66" t="n">
+        <v>5</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3845,6 +6652,51 @@
       <c r="J66" t="inlineStr">
         <is>
           <t>ID unique and stored</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Member ID creation: Generate member ID. AC: ID unique and stored.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>report_id,run_at,status,metrics</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>GET /reports, POST /reports/run</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3869,10 +6721,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E67" t="n">
+        <v>3</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3897,6 +6747,51 @@
       <c r="J67" t="inlineStr">
         <is>
           <t>CRM updated within SLA</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Provisioning sync: Sync ID to CRM. AC: CRM updated within SLA.</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>report_id,run_at,status,metrics</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>GET /reports, POST /reports/run</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3921,10 +6816,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E68" t="n">
+        <v>2</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3949,6 +6842,51 @@
       <c r="J68" t="inlineStr">
         <is>
           <t>PDF linked to member</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Welcome packet: Generate welcome PDF. AC: PDF linked to member.</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>document_type,file_name,file_size,upload_status</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>POST /documents, GET /documents/{id}</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -3973,10 +6911,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E69" t="n">
+        <v>2</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4001,6 +6937,51 @@
       <c r="J69" t="inlineStr">
         <is>
           <t>Audit entry created</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Provisioning audit: Log provisioning events. AC: Audit entry created.</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4025,10 +7006,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E70" t="n">
+        <v>5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4053,6 +7032,51 @@
       <c r="J70" t="inlineStr">
         <is>
           <t>User sees reason and next steps</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Rejection workflow: Handle payer rejection. AC: User sees reason and next steps.</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>member_id,eligibility_status,reason_code</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>POST /eligibility/check, POST /eligibility/submit</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4077,10 +7101,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E71" t="n">
+        <v>3</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4105,6 +7127,51 @@
       <c r="J71" t="inlineStr">
         <is>
           <t>Resubmission uses same app id</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Resubmission: Allow resubmission. AC: Resubmission uses same app id.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>member_id,eligibility_status,reason_code</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>POST /eligibility/check, POST /eligibility/submit</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4129,10 +7196,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E72" t="n">
+        <v>2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4157,6 +7222,51 @@
       <c r="J72" t="inlineStr">
         <is>
           <t>Email includes reason</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Rejection notifications: Notify on rejection. AC: Email includes reason.</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>channel,email,phone,template_id</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>POST /notifications/send, GET /notifications/{id}</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4181,10 +7291,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E73" t="n">
+        <v>2</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4209,6 +7317,51 @@
       <c r="J73" t="inlineStr">
         <is>
           <t>Audit includes old and new status</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Resubmit audit: Log resubmissions. AC: Audit includes old and new status.</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4233,10 +7386,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E74" t="n">
+        <v>5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4261,6 +7412,51 @@
       <c r="J74" t="inlineStr">
         <is>
           <t>Draft saved on timeout</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Auto-save on timeout: Auto-save on inactivity. AC: Draft saved on timeout.</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4285,10 +7481,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E75" t="n">
+        <v>3</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4313,6 +7507,51 @@
       <c r="J75" t="inlineStr">
         <is>
           <t>Draft expires after policy</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Draft retention: Retain draft for 30 days. AC: Draft expires after policy.</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4337,10 +7576,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E76" t="n">
+        <v>2</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4365,6 +7602,51 @@
       <c r="J76" t="inlineStr">
         <is>
           <t>Warning displayed at 2 minutes</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Session warning: Warn before timeout. AC: Warning displayed at 2 minutes.</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>channel,email,phone,template_id</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>POST /notifications/send, GET /notifications/{id}</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4389,10 +7671,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E77" t="n">
+        <v>3</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4417,6 +7697,51 @@
       <c r="J77" t="inlineStr">
         <is>
           <t>Draft restored accurately</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Resume draft: Resume draft from dashboard. AC: Draft restored accurately.</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>first_name,last_name,dob,ssn,email,phone,address,city,state,zip</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>POST /members, GET /members, GET /members/{id}, PUT /members/{id}</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4441,10 +7766,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E78" t="n">
+        <v>5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4469,6 +7792,51 @@
       <c r="J78" t="inlineStr">
         <is>
           <t>No PII in log output</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>PII masking logs: Mask PII in logs. AC: No PII in log output.</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4493,10 +7861,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E79" t="n">
+        <v>3</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4521,6 +7887,51 @@
       <c r="J79" t="inlineStr">
         <is>
           <t>Masked view for CSR</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>PII masking UI: Mask PII on screen. AC: Masked view for CSR.</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4545,10 +7956,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E80" t="n">
+        <v>3</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4573,6 +7982,51 @@
       <c r="J80" t="inlineStr">
         <is>
           <t>Audit includes user and reason</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Access logging: Log PII access. AC: Audit includes user and reason.</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4597,10 +8051,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E81" t="n">
+        <v>2</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4625,6 +8077,51 @@
       <c r="J81" t="inlineStr">
         <is>
           <t>CSP and HSTS enabled</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Security headers: Add security headers. AC: CSP and HSTS enabled.</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4649,10 +8146,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E82" t="n">
+        <v>3</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4677,6 +8172,51 @@
       <c r="J82" t="inlineStr">
         <is>
           <t>Cache hit rate tracked</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Eligibility caching: Cache eligibility calls. AC: Cache hit rate tracked.</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>report_id,run_at,status,metrics</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>GET /reports, POST /reports/run</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4701,10 +8241,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E83" t="n">
+        <v>3</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4729,6 +8267,51 @@
       <c r="J83" t="inlineStr">
         <is>
           <t>Alerts triggered over threshold</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>API latency alerts: Alert on slow APIs. AC: Alerts triggered over threshold.</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>report_id,run_at,status,metrics</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>GET /reports, POST /reports/run</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4753,10 +8336,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E84" t="n">
+        <v>5</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4781,6 +8362,51 @@
       <c r="J84" t="inlineStr">
         <is>
           <t>P95 under 2s</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Load testing baseline: Define load baseline. AC: P95 under 2s.</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>report_id,run_at,status,metrics</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>GET /reports, POST /reports/run</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4805,10 +8431,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E85" t="n">
+        <v>2</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -4833,6 +8457,51 @@
       <c r="J85" t="inlineStr">
         <is>
           <t>Query time improved</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Database indexing: Optimize indexes. AC: Query time improved.</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>report_id,run_at,status,metrics</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>GET /reports, POST /reports/run</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4857,10 +8526,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E86" t="n">
+        <v>5</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -4885,6 +8552,51 @@
       <c r="J86" t="inlineStr">
         <is>
           <t>Export contains required events</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Audit export: Export audit logs. AC: Export contains required events.</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4909,10 +8621,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E87" t="n">
+        <v>3</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -4937,6 +8647,51 @@
       <c r="J87" t="inlineStr">
         <is>
           <t>Schedules run on time</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Export scheduling: Schedule exports. AC: Schedules run on time.</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>report_id,run_at,status,metrics</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>GET /reports, POST /reports/run</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -4961,10 +8716,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E88" t="n">
+        <v>2</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -4989,6 +8742,51 @@
       <c r="J88" t="inlineStr">
         <is>
           <t>Filters applied to export</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Export filters: Filter by date and type. AC: Filters applied to export.</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>report_id,run_at,status,metrics</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>GET /reports, POST /reports/run</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -5013,10 +8811,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E89" t="n">
+        <v>2</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -5041,6 +8837,51 @@
       <c r="J89" t="inlineStr">
         <is>
           <t>Email sent on completion</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Export notification: Notify when export complete. AC: Email sent on completion.</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>channel,email,phone,template_id</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>POST /notifications/send, GET /notifications/{id}</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -5065,10 +8906,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E90" t="n">
+        <v>5</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -5093,6 +8932,51 @@
       <c r="J90" t="inlineStr">
         <is>
           <t>Preferences saved and applied</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Notification preferences: User manages preferences. AC: Preferences saved and applied.</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>channel,email,phone,template_id</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>POST /notifications/send, GET /notifications/{id}</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -5117,10 +9001,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E91" t="n">
+        <v>3</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -5145,6 +9027,51 @@
       <c r="J91" t="inlineStr">
         <is>
           <t>SMS failure triggers email</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Channel fallback: Fallback to email. AC: SMS failure triggers email.</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>channel,email,phone,template_id</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>POST /notifications/send, GET /notifications/{id}</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -5169,10 +9096,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E92" t="n">
+        <v>2</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -5197,6 +9122,51 @@
       <c r="J92" t="inlineStr">
         <is>
           <t>Templates require approval</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Template governance: Approve templates. AC: Templates require approval.</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>channel,email,phone,template_id</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>POST /notifications/send, GET /notifications/{id}</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -5221,10 +9191,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E93" t="n">
+        <v>2</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -5249,6 +9217,51 @@
       <c r="J93" t="inlineStr">
         <is>
           <t>Audit entry created</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Preference audit: Log preference updates. AC: Audit entry created.</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -5273,10 +9286,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E94" t="n">
+        <v>5</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -5301,6 +9312,51 @@
       <c r="J94" t="inlineStr">
         <is>
           <t>Data retained per policy</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Retention policy: Enforce retention rules. AC: Data retained per policy.</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -5325,10 +9381,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E95" t="n">
+        <v>3</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -5353,6 +9407,51 @@
       <c r="J95" t="inlineStr">
         <is>
           <t>Deletion workflow initiated</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Deletion request: Request deletion. AC: Deletion workflow initiated.</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -5377,10 +9476,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E96" t="n">
+        <v>3</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5405,6 +9502,51 @@
       <c r="J96" t="inlineStr">
         <is>
           <t>Held records excluded</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Legal hold: Apply legal hold. AC: Held records excluded.</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -5429,10 +9571,8 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E97" t="n">
+        <v>2</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5457,6 +9597,51 @@
       <c r="J97" t="inlineStr">
         <is>
           <t>Audit includes requestor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Deletion audit: Audit deletions. AC: Audit includes requestor.</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -5481,10 +9666,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E98" t="n">
+        <v>5</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -5509,6 +9692,51 @@
       <c r="J98" t="inlineStr">
         <is>
           <t>All critical paths pass</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Cross-module regression: Run full regression. AC: All critical paths pass.</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>report_id,run_at,status,metrics</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>GET /reports, POST /reports/run</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -5533,10 +9761,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E99" t="n">
+        <v>5</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -5561,6 +9787,51 @@
       <c r="J99" t="inlineStr">
         <is>
           <t>No critical findings</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Security hardening: Complete security review. AC: No critical findings.</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>actor_id,action,timestamp,source</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>GET /audit/events</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -5585,10 +9856,8 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="E100" t="n">
+        <v>5</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -5613,6 +9882,51 @@
       <c r="J100" t="inlineStr">
         <is>
           <t>P95 under SLA</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Performance validation: Validate performance. AC: P95 under SLA.</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>report_id,run_at,status,metrics</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>GET /reports, POST /reports/run</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
@@ -5637,10 +9951,8 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E101" t="n">
+        <v>3</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -5665,6 +9977,51 @@
       <c r="J101" t="inlineStr">
         <is>
           <t>Runbooks approved</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Operational readiness: Finalize runbooks. AC: Runbooks approved.</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>report_id,run_at,status,metrics</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>GET /reports, POST /reports/run</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Validate required fields; enforce format/length rules; persist audit trail.</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Show user-friendly error; log failure; allow retry where applicable.</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>PII masking, RBAC checks, audit logging, secure storage.</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Use valid and invalid datasets; include boundary values.</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Downstream services, audit logging, notification service as applicable.</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Field list and exact validation rules derived from UI/spec when available.</t>
         </is>
       </c>
     </row>
